--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488122_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488122_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7557</v>
+        <v>3.3905</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2179</v>
+        <v>5.1359</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5379</v>
+        <v>-1.7454</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.6707</v>
+        <v>5.9172</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.5004</v>
+        <v>-0.6147</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1703</v>
+        <v>6.5319</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2369</v>
+        <v>6.4352</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6509</v>
+        <v>0.3165</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8878</v>
+        <v>6.1187</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9076</v>
+        <v>-0.518</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8495</v>
+        <v>-0.9312</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0581</v>
+        <v>0.4132</v>
       </c>
       <c r="P2" t="n">
         <v>1.5858</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R2" t="n">
-        <v>3.568</v>
+        <v>2.5769</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5673</v>
+        <v>-0.5616</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8306</v>
+        <v>-0.3082</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7366</v>
+        <v>-0.2534</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2734</v>
+        <v>-3.5509</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1326</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1408</v>
+        <v>-3.5509</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1762</v>
+        <v>3.3686</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2585</v>
+        <v>0.8978</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0823</v>
+        <v>2.4709</v>
       </c>
       <c r="G3" t="n">
-        <v>5.9172</v>
+        <v>-1.6707</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6147</v>
+        <v>-1.5004</v>
       </c>
       <c r="I3" t="n">
-        <v>6.5319</v>
+        <v>-0.1703</v>
       </c>
       <c r="J3" t="n">
-        <v>6.4352</v>
+        <v>0.2369</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3165</v>
+        <v>-0.6509</v>
       </c>
       <c r="L3" t="n">
-        <v>6.1187</v>
+        <v>0.8878</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.518</v>
+        <v>-1.9076</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9312</v>
+        <v>-0.8495</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4132</v>
+        <v>-1.0581</v>
       </c>
       <c r="P3" t="n">
         <v>1.5858</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5769</v>
+        <v>3.568</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7759</v>
+        <v>1.1802</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1855</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5903</v>
+        <v>0.6697</v>
       </c>
       <c r="V3" t="n">
-        <v>-3.5509</v>
+        <v>2.2734</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.1326</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.5509</v>
+        <v>0.1408</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2835</v>
+        <v>1.0966</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5108</v>
+        <v>1.0431</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2273</v>
+        <v>0.0535</v>
       </c>
       <c r="G4" t="n">
         <v>2.8193</v>
@@ -766,13 +766,13 @@
         <v>3.3698</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0204</v>
+        <v>-0.2074</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8074</v>
+        <v>-0.2751</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.213</v>
+        <v>0.0677</v>
       </c>
       <c r="V4" t="n">
         <v>0.0704</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. GARCIA JIMENEZ</t>
+          <t>A. GONZALEZ PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5053</v>
+        <v>0.1552</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8461</v>
+        <v>0.6203</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3409</v>
+        <v>-0.4651</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3834</v>
+        <v>-0.3993</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.655</v>
+        <v>0.5457</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2717</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.659</v>
+        <v>2.0498</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.659</v>
+        <v>1.3992</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.6506</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2756</v>
+        <v>-2.4491</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0039</v>
+        <v>-0.8534</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2717</v>
+        <v>-1.5957</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.1716</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1219</v>
+        <v>-0.278</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1872</v>
+        <v>-0.5642</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0653</v>
+        <v>0.2861</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.3479</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1258</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PEREZ</t>
+          <t>O. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7533</v>
+        <v>-0.5614</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6251</v>
+        <v>-0.8461</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1282</v>
+        <v>0.2847</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3993</v>
+        <v>-0.3834</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5457</v>
+        <v>-0.655</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9451000000000001</v>
+        <v>0.2717</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0498</v>
+        <v>-0.659</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3992</v>
+        <v>-0.659</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6506</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4491</v>
+        <v>0.2756</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8534</v>
+        <v>0.0039</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5957</v>
+        <v>0.2717</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1716</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1864</v>
+        <v>-0.1781</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.8095</v>
+        <v>-0.1872</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6231</v>
+        <v>0.0091</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3479</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1258</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>F. GARCIA GARRIDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8198</v>
+        <v>-0.6162</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8428</v>
+        <v>-0.7708</v>
       </c>
       <c r="F7" t="n">
-        <v>0.023</v>
+        <v>0.1546</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.932</v>
+        <v>-1.2128</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4385</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4935</v>
+        <v>-0.4018</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3275</v>
+        <v>-0.6791</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6924</v>
+        <v>-0.6791</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6351</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6046</v>
+        <v>-0.5337</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7461</v>
+        <v>-0.1319</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1415</v>
+        <v>-0.4018</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7247</v>
+        <v>0.0019</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4847</v>
+        <v>-0.0917</v>
       </c>
       <c r="U7" t="n">
-        <v>0.24</v>
+        <v>0.0936</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. GARCIA GARRIDO</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0799</v>
+        <v>-1.2709</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1783</v>
+        <v>-1.1254</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0984</v>
+        <v>-0.1455</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2128</v>
+        <v>-2.932</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-2.4385</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4018</v>
+        <v>-0.4935</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6791</v>
+        <v>-1.3275</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6791</v>
+        <v>-0.6924</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.6351</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5337</v>
+        <v>-1.6046</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1319</v>
+        <v>-1.7461</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4018</v>
+        <v>0.1415</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4617</v>
+        <v>0.2735</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4992</v>
+        <v>0.202</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0374</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3685</v>
+        <v>-2.0719</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7278</v>
+        <v>-2.9086</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3593</v>
+        <v>0.8366</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6301</v>
@@ -1156,13 +1156,13 @@
         <v>2.9733</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5333</v>
+        <v>-0.2367</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3709</v>
+        <v>0.1901</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9042</v>
+        <v>-0.4269</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1962</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0343</v>
+        <v>-2.9623</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5693</v>
+        <v>-2.9746</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.465</v>
+        <v>0.0124</v>
       </c>
       <c r="G10" t="n">
         <v>-4.3367</v>
@@ -1234,13 +1234,13 @@
         <v>3.9645</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.2328</v>
+        <v>-1.1608</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1194</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1135</v>
+        <v>-0.6361</v>
       </c>
       <c r="V10" t="n">
         <v>1.5441</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8085</v>
+        <v>-5.7461</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3623</v>
+        <v>-4.2999</v>
       </c>
       <c r="F11" t="n">
         <v>-1.4462</v>
@@ -1312,10 +1312,10 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0221</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2534</v>
+        <v>0.3158</v>
       </c>
       <c r="U11" t="n">
         <v>-0.2313</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.1542</v>
+        <v>-5.2179</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.1645</v>
+        <v>-5.228299999999999</v>
       </c>
       <c r="F12" t="n">
         <v>0.01049999999999995</v>
@@ -1390,13 +1390,13 @@
         <v>22.7957</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0183</v>
+        <v>-1.0825</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6686</v>
+        <v>-0.7325999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3499</v>
+        <v>-0.3499999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-2.218</v>
@@ -1405,7 +1405,7 @@
         <v>6.3425</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.560599999999999</v>
+        <v>-8.560600000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6744</v>
+        <v>5.28</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0249</v>
+        <v>4.7193</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6495</v>
+        <v>0.5607</v>
       </c>
       <c r="G13" t="n">
         <v>5.1469</v>
@@ -1468,13 +1468,13 @@
         <v>2.1805</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8376</v>
+        <v>0.4432</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.3149</v>
       </c>
       <c r="U13" t="n">
-        <v>0.217</v>
+        <v>0.1282</v>
       </c>
       <c r="V13" t="n">
         <v>0.4828</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8112</v>
+        <v>3.799</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8336</v>
+        <v>3.528</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9776</v>
+        <v>0.2711</v>
       </c>
       <c r="G14" t="n">
         <v>0.4102</v>
@@ -1546,13 +1546,13 @@
         <v>1.784</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1143</v>
+        <v>1.1021</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.3259</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4827</v>
+        <v>0.7762</v>
       </c>
       <c r="V14" t="n">
         <v>1.4938</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8682</v>
+        <v>3.175</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3883</v>
+        <v>3.5458</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4798</v>
+        <v>-0.3708</v>
       </c>
       <c r="G15" t="n">
-        <v>3.733</v>
+        <v>1.3787</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3957</v>
+        <v>3.6019</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3373</v>
+        <v>-2.2233</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4835</v>
+        <v>3.0132</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8367</v>
+        <v>3.6522</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6467000000000001</v>
+        <v>-0.639</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2495</v>
+        <v>-1.6346</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5590000000000001</v>
+        <v>-0.0503</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6905</v>
+        <v>-1.5843</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R15" t="n">
-        <v>1.784</v>
+        <v>1.9822</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0739</v>
+        <v>-0.2809</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6116</v>
+        <v>-0.166</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4623</v>
+        <v>-0.1149</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7494</v>
+        <v>2.0772</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2666</v>
+        <v>2.6808</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.016</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1648</v>
+        <v>2.6457</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0364</v>
+        <v>0.1659</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8716</v>
+        <v>2.4798</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3787</v>
+        <v>3.733</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6019</v>
+        <v>2.3957</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.2233</v>
+        <v>1.3373</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0132</v>
+        <v>2.4835</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6522</v>
+        <v>1.8367</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.639</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6346</v>
+        <v>1.2495</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0503</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5843</v>
+        <v>0.6905</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9822</v>
+        <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2911</v>
+        <v>0.8515</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6753</v>
+        <v>0.3892</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6157</v>
+        <v>0.4623</v>
       </c>
       <c r="V16" t="n">
-        <v>2.0772</v>
+        <v>-0.7494</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6808</v>
+        <v>0.2666</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6036</v>
+        <v>-1.016</v>
       </c>
     </row>
     <row r="17">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3529</v>
+        <v>0.5671</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3844</v>
+        <v>-0.2825</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7373</v>
+        <v>0.8496</v>
       </c>
       <c r="G18" t="n">
         <v>1.1284</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.2891</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0403</v>
+        <v>0.0615</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1152</v>
+        <v>0.2275</v>
       </c>
       <c r="V18" t="n">
         <v>0.1408</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1621</v>
+        <v>0.1994</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4618</v>
+        <v>-1.5449</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2997</v>
+        <v>1.7444</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9959</v>
@@ -1936,13 +1936,13 @@
         <v>3.1716</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2147</v>
+        <v>0.1468</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0901</v>
+        <v>-0.1732</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1247</v>
+        <v>0.32</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1408</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6137</v>
+        <v>-2.9193</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.1378</v>
+        <v>-4.4434</v>
       </c>
       <c r="F20" t="n">
         <v>1.5241</v>
@@ -2014,10 +2014,10 @@
         <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3634</v>
+        <v>0.0577</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3782</v>
+        <v>0.0726</v>
       </c>
       <c r="U20" t="n">
         <v>-0.0148</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9767</v>
+        <v>-3.5706</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4628</v>
+        <v>-2.3609</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5139</v>
+        <v>-1.2096</v>
       </c>
       <c r="G21" t="n">
         <v>-2.7548</v>
@@ -2092,13 +2092,13 @@
         <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4382</v>
+        <v>-0.0321</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.11</v>
+        <v>-0.0081</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3283</v>
+        <v>-0.024</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3873</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0782</v>
+        <v>-4.4566</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.9603</v>
+        <v>-5.4509</v>
       </c>
       <c r="F22" t="n">
-        <v>0.882</v>
+        <v>0.9944</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3276</v>
@@ -2170,13 +2170,13 @@
         <v>2.1805</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5014999999999999</v>
+        <v>0.1201</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.4669</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4748</v>
+        <v>0.5871</v>
       </c>
       <c r="V22" t="n">
         <v>-0.4828</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.154099999999999</v>
+        <v>6.833</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.01060000000000194</v>
+        <v>-0.01029999999999998</v>
       </c>
       <c r="F23" t="n">
-        <v>6.1645</v>
+        <v>6.843699999999999</v>
       </c>
       <c r="G23" t="n">
         <v>8.855399999999999</v>
@@ -2248,13 +2248,13 @@
         <v>15.8579</v>
       </c>
       <c r="S23" t="n">
-        <v>2.0186</v>
+        <v>2.6975</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3498999999999994</v>
+        <v>0.3499</v>
       </c>
       <c r="U23" t="n">
-        <v>1.6685</v>
+        <v>2.3476</v>
       </c>
       <c r="V23" t="n">
         <v>2.218</v>
